--- a/assets/template.xlsx
+++ b/assets/template.xlsx
@@ -840,7 +840,7 @@
     <mergeCell ref="B46:D47"/>
   </mergeCells>
   <pageMargins left="0.008421985815602837" right="0.008421985815602837" top="0.45" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait" scale="57"/>
+  <pageSetup xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdPS" orientation="portrait" scale="57"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;RElectronically signed:_x000a_[Full Name, degrees]_x000a_&amp;D, &amp;T</oddFooter>
